--- a/smartshop/EvidenceBasedAdaptiveUI/reports/Statistical_Validation/tables/moderate_evidence.xlsx
+++ b/smartshop/EvidenceBasedAdaptiveUI/reports/Statistical_Validation/tables/moderate_evidence.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S14"/>
+  <dimension ref="A1:S13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -537,22 +537,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>65.66197244947071</v>
+        <v>68.50432172022388</v>
       </c>
       <c r="D2" t="n">
         <v>35</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001286183419324869</v>
+        <v>0.0006037664252750105</v>
       </c>
       <c r="F2" t="n">
-        <v>0.421868161538557</v>
+        <v>0.1980353874902034</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05273352019231962</v>
+        <v>0.02475442343627543</v>
       </c>
       <c r="H2" t="n">
-        <v>0.256245921820174</v>
+        <v>0.247314724520166</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -560,7 +560,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K2" t="b">
         <v>0</v>
@@ -569,7 +569,7 @@
         <v>1</v>
       </c>
       <c r="M2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N2" t="n">
         <v>1</v>
@@ -589,7 +589,7 @@
         <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>0.001286183419324869</v>
+        <v>0.0006037664252750105</v>
       </c>
     </row>
     <row r="3">
@@ -600,26 +600,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>desktop_search_visibility</t>
+          <t>mobile_sticky_header</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>23.86590646617123</v>
+        <v>14.5405572774308</v>
       </c>
       <c r="D3" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04755964831037239</v>
+        <v>0.04236106665679771</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6057833930732491</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4395340095133445</v>
+        <v>0.4342009332321765</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2442637225734269</v>
+        <v>0.2547806941889191</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -627,7 +627,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K3" t="b">
         <v>0</v>
@@ -639,7 +639,7 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8489401726858951</v>
+        <v>0.8704897822446489</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -656,13 +656,13 @@
         <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>0.04755964831037239</v>
+        <v>0.04236106665679771</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Neuroticism_Level</t>
+          <t>primary_device</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -671,22 +671,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>23.18817882088389</v>
+        <v>12.18164420537235</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01007289052385354</v>
+        <v>0.03238184657806457</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5892074934687138</v>
+        <v>0.6057833930732491</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4129885114779952</v>
+        <v>0.4370180808844971</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2407705277898641</v>
+        <v>0.2332002148424292</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K4" t="b">
         <v>0</v>
@@ -706,7 +706,7 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8655227202133037</v>
+        <v>0.8429996990577381</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>0.01007289052385354</v>
+        <v>0.03238184657806457</v>
       </c>
     </row>
     <row r="5">
@@ -734,26 +734,26 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mobile_product_card</t>
+          <t>desktop_category_display</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>45.84472373991052</v>
+        <v>33.80211705015776</v>
       </c>
       <c r="D5" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01808408902555184</v>
+        <v>0.03804560723180549</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6057833930732491</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3707238250238127</v>
+        <v>0.4342009332321765</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2393865173206046</v>
+        <v>0.2242783302503334</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K5" t="b">
         <v>0</v>
@@ -773,7 +773,7 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8736398889490427</v>
+        <v>0.8293622354354354</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>0.01808408902555184</v>
+        <v>0.03804560723180549</v>
       </c>
     </row>
     <row r="6">
@@ -801,26 +801,26 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>desktop_category_display</t>
+          <t>mobile_product_card</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>33.650420437344</v>
+        <v>44.35431867020466</v>
       </c>
       <c r="D6" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03948431736169739</v>
+        <v>0.02562016680233264</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6057833930732491</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4395340095133445</v>
+        <v>0.4342009332321765</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2368206791271404</v>
+        <v>0.2224917701883998</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K6" t="b">
         <v>0</v>
@@ -840,7 +840,7 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0.8414788715893061</v>
+        <v>0.8312914079845187</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>0.03948431736169739</v>
+        <v>0.02562016680233264</v>
       </c>
     </row>
     <row r="7">
@@ -872,22 +872,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>31.39106946323544</v>
+        <v>32.1841524208596</v>
       </c>
       <c r="D7" t="n">
         <v>15</v>
       </c>
       <c r="E7" t="n">
-        <v>0.007784440760364039</v>
+        <v>0.006076529755922339</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5892074934687138</v>
+        <v>0.6057833930732491</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1595810355874628</v>
+        <v>0.1673443007117269</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2287322651166477</v>
+        <v>0.2188448856144747</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K7" t="b">
         <v>0</v>
@@ -907,7 +907,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0.9269018048245539</v>
+        <v>0.9146708149917904</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -924,37 +924,37 @@
         <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>0.007784440760364039</v>
+        <v>0.006076529755922339</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>Neuroticism_Level</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>color_theme_pref</t>
+          <t>button_style_pref</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>48.45276345166277</v>
+        <v>21.27011268026897</v>
       </c>
       <c r="D8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E8" t="n">
-        <v>0.003290526498034538</v>
+        <v>0.01928683302746032</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5396463456776642</v>
+        <v>0.6057833930732491</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1349115864194161</v>
+        <v>0.3953800770629365</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2201198842714187</v>
+        <v>0.2178943094481499</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K8" t="b">
         <v>0</v>
@@ -974,7 +974,7 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0.9240659301618951</v>
+        <v>0.8389761699752223</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -991,37 +991,37 @@
         <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>0.003290526498034538</v>
+        <v>0.01928683302746032</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Agreeableness_Level</t>
+          <t>primary_device</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>button_style_pref</t>
+          <t>social_proof_display</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>19.22358129100138</v>
+        <v>10.56183481569735</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03751305597841784</v>
+        <v>0.03195580725403268</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6057833930732491</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7192283768587451</v>
+        <v>0.4370180808844971</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2192235234355644</v>
+        <v>0.2171429213314659</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K9" t="b">
         <v>0</v>
@@ -1041,7 +1041,7 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0.7324510745960361</v>
+        <v>0.8206912347577575</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1058,37 +1058,37 @@
         <v>1</v>
       </c>
       <c r="S9" t="n">
-        <v>0.03751305597841784</v>
+        <v>0.03195580725403268</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>primary_device</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>mobile_grid_pref</t>
+          <t>mobile_price_display</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>9.585975882803975</v>
+        <v>21.05260853833937</v>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>0.02243409391836799</v>
+        <v>0.02072969480257041</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6057833930732491</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5486315591051685</v>
+        <v>0.2833058289684623</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2189289369042381</v>
+        <v>0.2167773737572234</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K10" t="b">
         <v>0</v>
@@ -1108,7 +1108,7 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0.7894324882992878</v>
+        <v>0.8711345115542989</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1125,37 +1125,37 @@
         <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>0.02243409391836799</v>
+        <v>0.02072969480257041</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>Agreeableness_Level</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>mobile_price_display</t>
+          <t>button_style_pref</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>18.84612192927982</v>
+        <v>19.62573317382398</v>
       </c>
       <c r="D11" t="n">
         <v>10</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0422612621360954</v>
+        <v>0.03299809885565442</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6057833930732491</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5775705825266372</v>
+        <v>0.6361436320471427</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2170606017295621</v>
+        <v>0.2093022697443647</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K11" t="b">
         <v>0</v>
@@ -1175,7 +1175,7 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>0.7709587881797708</v>
+        <v>0.7485265190253044</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -1192,37 +1192,37 @@
         <v>1</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0422612621360954</v>
+        <v>0.03299809885565442</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Neuroticism_Level</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>checkout_style</t>
+          <t>mobile_whitespace</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>17.56380493892523</v>
+        <v>19.44250377428342</v>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E12" t="n">
-        <v>0.02474531586029017</v>
+        <v>0.03498911993653327</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6057833930732491</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5006317894422778</v>
+        <v>0.358638479349466</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2095459671463831</v>
+        <v>0.2083229366266225</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K12" t="b">
         <v>0</v>
@@ -1242,7 +1242,7 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>0.7902203425447025</v>
+        <v>0.8312154939217499</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1259,37 +1259,37 @@
         <v>1</v>
       </c>
       <c r="S12" t="n">
-        <v>0.02474531586029017</v>
+        <v>0.03498911993653327</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>primary_device</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>desktop_navigation</t>
+          <t>color_theme_pref</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>8.393373537164944</v>
+        <v>45.09188072435776</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="E13" t="n">
-        <v>0.038544379976584</v>
+        <v>0.008163136620084241</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6151665697823192</v>
+        <v>0.6057833930732491</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5486315591051685</v>
+        <v>0.1673443007117269</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2048581648014663</v>
+        <v>0.2006504617228805</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K13" t="b">
         <v>0</v>
@@ -1309,7 +1309,7 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>0.7641638402890324</v>
+        <v>0.8884775696395767</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -1326,74 +1326,7 @@
         <v>1</v>
       </c>
       <c r="S13" t="n">
-        <v>0.038544379976584</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Openness_Level</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>mobile_product_card</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>16.05607182887269</v>
-      </c>
-      <c r="D14" t="n">
-        <v>8</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.04158454723497933</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.6151665697823192</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.5135785999327165</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.2003501424311491</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
-        <v>200</v>
-      </c>
-      <c r="K14" t="b">
-        <v>0</v>
-      </c>
-      <c r="L14" t="b">
-        <v>1</v>
-      </c>
-      <c r="M14" t="b">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0.7675127603256419</v>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>Moderate Statistical Evidence</t>
-        </is>
-      </c>
-      <c r="P14" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="b">
-        <v>1</v>
-      </c>
-      <c r="R14" t="b">
-        <v>1</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0.04158454723497933</v>
+        <v>0.008163136620084241</v>
       </c>
     </row>
   </sheetData>
